--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_26.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_26.xlsx
@@ -471,98 +471,98 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64422</v>
+        <v>24574</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Marina Martins</t>
+          <t>Emanuella Porto</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>45096</v>
       </c>
       <c r="G2" t="n">
-        <v>11616.05</v>
+        <v>4526.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79470</v>
+        <v>28811</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Danilo da Mata</t>
+          <t>Sra. Clara Vieira</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45078</v>
+        <v>45098</v>
       </c>
       <c r="G3" t="n">
-        <v>3143.32</v>
+        <v>5689.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1056</v>
+        <v>28010</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Luiz Miguel Silva</t>
+          <t>Larissa da Rosa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45080</v>
+        <v>45079</v>
       </c>
       <c r="G4" t="n">
-        <v>12145.26</v>
+        <v>10890.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18145</v>
+        <v>56843</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fernanda Rocha</t>
+          <t>Srta. Lavínia da Conceição</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -572,84 +572,84 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45099</v>
+        <v>45100</v>
       </c>
       <c r="G5" t="n">
-        <v>9261.190000000001</v>
+        <v>11400.24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>38840</v>
+        <v>94519</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Davi Luiz Barbosa</t>
+          <t>Juliana da Mota</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45100</v>
+        <v>45082</v>
       </c>
       <c r="G6" t="n">
-        <v>10240.58</v>
+        <v>5734.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>39537</v>
+        <v>63656</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kevin Cardoso</t>
+          <t>Luiz Fernando Azevedo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>4</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45083</v>
+        <v>45103</v>
       </c>
       <c r="G7" t="n">
-        <v>8839.700000000001</v>
+        <v>12178.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>13257</v>
+        <v>67711</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Clara Viana</t>
+          <t>Francisco Mendes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -659,60 +659,60 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45093</v>
+        <v>45100</v>
       </c>
       <c r="G8" t="n">
-        <v>8275.33</v>
+        <v>11607.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>53590</v>
+        <v>51503</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Helena Farias</t>
+          <t>Luna Vieira</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>7</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45092</v>
+        <v>45082</v>
       </c>
       <c r="G9" t="n">
-        <v>7705.23</v>
+        <v>11686.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>28730</v>
+        <v>25418</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Antônio Barbosa</t>
+          <t>Bruno Almeida</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -721,42 +721,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45078</v>
+        <v>45092</v>
       </c>
       <c r="G10" t="n">
-        <v>9544.780000000001</v>
+        <v>8789.440000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94771</v>
+        <v>14044</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thomas Peixoto</t>
+          <t>João Miguel Cardoso</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45084</v>
+        <v>45096</v>
       </c>
       <c r="G11" t="n">
-        <v>8488.58</v>
+        <v>4041.48</v>
       </c>
     </row>
   </sheetData>
